--- a/backend/data/financials_by_company/000819.SZ.xlsx
+++ b/backend/data/financials_by_company/000819.SZ.xlsx
@@ -4016,182 +4016,182 @@
       </c>
       <c r="DB1" t="inlineStr">
         <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="EL1" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Yueyang Xingchang Petro-Chemical Co., Ltd. engages in the development, production, sales, and retail of petrochemical products in China. It offers methyl tert-butyl ether, liquefied petroleum gas, propylene, industrial isooctane, o-cresol, new chemical materials, energy conservation and environmental protection, energy chemicals, etc. The company was founded in 1989 and is based in Yueyang, China.</t>
+          <t>Yueyang Xingchang Petro-Chemical Co., Ltd. engages in the production and sale of chemical products in China. It offers methyl tert-butyl ether, liquefied petroleum gas, propylene, industrial isooctane, o-cresol, calcined petroleum coke, specialty polypropylene, synthetic materials, and petroleum and plastic products. The company also provides energy and chemical, new chemical materials, refined oil, and other products. In addition, it is involved in research and development of special catalyst technologies, catalyst application development, and the development of new polyolefin products. Yueyang Xingchang Petro-Chemical Co., Ltd. was founded in 1989 and is headquartered in Yueyang, China.</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -4286,34 +4286,34 @@
         <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>13.26</v>
+        <v>11.66</v>
       </c>
       <c r="T2" t="n">
-        <v>13.3</v>
+        <v>12.4</v>
       </c>
       <c r="U2" t="n">
-        <v>12.65</v>
+        <v>11.66</v>
       </c>
       <c r="V2" t="n">
-        <v>13.28</v>
+        <v>12.05</v>
       </c>
       <c r="W2" t="n">
-        <v>13.26</v>
+        <v>11.66</v>
       </c>
       <c r="X2" t="n">
-        <v>13.3</v>
+        <v>12.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>12.65</v>
+        <v>11.66</v>
       </c>
       <c r="Z2" t="n">
-        <v>13.28</v>
+        <v>12.05</v>
       </c>
       <c r="AA2" t="n">
         <v>0.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="AC2" t="n">
         <v>1752192000</v>
@@ -4325,37 +4325,37 @@
         <v>0.37</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.497</v>
+        <v>0.529</v>
       </c>
       <c r="AG2" t="n">
-        <v>6543861</v>
+        <v>3563400</v>
       </c>
       <c r="AH2" t="n">
-        <v>6543861</v>
+        <v>3563400</v>
       </c>
       <c r="AI2" t="n">
-        <v>8023187</v>
+        <v>8240484</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5945782</v>
+        <v>5597495</v>
       </c>
       <c r="AK2" t="n">
-        <v>5945782</v>
+        <v>5597495</v>
       </c>
       <c r="AL2" t="n">
-        <v>13.05</v>
+        <v>11.93</v>
       </c>
       <c r="AM2" t="n">
-        <v>13.06</v>
+        <v>11.94</v>
       </c>
       <c r="AN2" t="n">
-        <v>4822033920</v>
+        <v>4404493824</v>
       </c>
       <c r="AO2" t="n">
-        <v>4899629749</v>
+        <v>4326897765</v>
       </c>
       <c r="AP2" t="n">
-        <v>12.65</v>
+        <v>11.12</v>
       </c>
       <c r="AQ2" t="n">
         <v>21</v>
@@ -4367,13 +4367,13 @@
         <v>2.246971</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.2914014</v>
+        <v>1.1795789</v>
       </c>
       <c r="AU2" t="n">
-        <v>15.4212</v>
+        <v>14.8174</v>
       </c>
       <c r="AV2" t="n">
-        <v>16.48085</v>
+        <v>16.24135</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -4390,7 +4390,7 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>5433087488</v>
+        <v>5015547392</v>
       </c>
       <c r="BB2" t="n">
         <v>-0.01684</v>
@@ -4402,7 +4402,7 @@
         <v>369504506</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.41612</v>
+        <v>0.39997002</v>
       </c>
       <c r="BF2" t="n">
         <v>0.019270001</v>
@@ -4414,7 +4414,7 @@
         <v>5.626</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.3195877</v>
+        <v>2.1187346</v>
       </c>
       <c r="BJ2" t="n">
         <v>1767139200</v>
@@ -4443,16 +4443,16 @@
         <v>1591920000</v>
       </c>
       <c r="BR2" t="n">
-        <v>1.455</v>
+        <v>1.343</v>
       </c>
       <c r="BS2" t="n">
-        <v>69.592</v>
+        <v>64.244</v>
       </c>
       <c r="BT2" t="n">
-        <v>-0.12877792</v>
+        <v>-0.22730285</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="BV2" t="n">
         <v>0.1</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="BY2" t="n">
-        <v>13.05</v>
+        <v>11.92</v>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
@@ -4570,135 +4570,135 @@
       </c>
       <c r="DB2" t="inlineStr">
         <is>
+          <t>Yueyang Xingchang Petro-Chemical Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="DC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DC2" t="n">
-        <v>1782111882</v>
-      </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DE2" t="n">
+        <v>1783062264</v>
+      </c>
+      <c r="DF2" t="inlineStr">
         <is>
           <t>SHZ</t>
         </is>
       </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DG2" t="inlineStr">
         <is>
           <t>finmb_5723123</t>
         </is>
       </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DH2" t="inlineStr">
         <is>
           <t>Asia/Shanghai</t>
         </is>
       </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DI2" t="inlineStr">
         <is>
           <t>CST</t>
         </is>
       </c>
-      <c r="DH2" t="n">
+      <c r="DJ2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DI2" t="inlineStr">
+      <c r="DK2" t="inlineStr">
         <is>
           <t>cn_market</t>
         </is>
       </c>
-      <c r="DJ2" t="b">
+      <c r="DL2" t="b">
         <v>0</v>
       </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>Yueyang Xingchang Petro-Chemical Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
+      <c r="DM2" t="n">
+        <v>2.2298477</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="DO2" t="inlineStr">
         <is>
           <t>YUEYANG XINGCHANG PETRO CHEMICA</t>
         </is>
       </c>
-      <c r="DM2" t="b">
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DQ2" t="b">
         <v>0</v>
       </c>
-      <c r="DN2" t="n">
+      <c r="DR2" t="n">
         <v>867202200000</v>
       </c>
-      <c r="DO2" t="n">
-        <v>-0.21000004</v>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>12.65 - 13.28</t>
-        </is>
-      </c>
-      <c r="DQ2" t="inlineStr">
+      <c r="DS2" t="n">
+        <v>0.26000023</v>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>11.66 - 12.05</t>
+        </is>
+      </c>
+      <c r="DU2" t="inlineStr">
         <is>
           <t>Shenzhen</t>
         </is>
       </c>
-      <c r="DR2" t="n">
-        <v>8023187</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0.40000057</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>0.0316206</v>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>12.65 - 21.0</t>
-        </is>
-      </c>
       <c r="DV2" t="n">
-        <v>-7.95</v>
+        <v>8240484</v>
       </c>
       <c r="DW2" t="n">
-        <v>-0.37857142</v>
+        <v>0.8000002000000001</v>
       </c>
       <c r="DX2" t="n">
-        <v>-12.877792</v>
-      </c>
-      <c r="DY2" t="n">
+        <v>0.07194246</v>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>11.12 - 21.0</t>
+        </is>
+      </c>
+      <c r="DZ2" t="n">
+        <v>-9.08</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>-0.43238094</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>-22.730286</v>
+      </c>
+      <c r="EC2" t="n">
         <v>1619607540</v>
       </c>
-      <c r="DZ2" t="n">
+      <c r="ED2" t="n">
         <v>1619607540</v>
       </c>
-      <c r="EA2" t="n">
+      <c r="EE2" t="n">
         <v>-0.17</v>
       </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="EC2" t="n">
-        <v>-2.3711996</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>-0.15376233</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>-3.43085</v>
-      </c>
       <c r="EF2" t="n">
-        <v>-0.2081719</v>
+        <v>-2.8974</v>
       </c>
       <c r="EG2" t="n">
+        <v>-0.19554037</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>-4.32135</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>-0.26607087</v>
+      </c>
+      <c r="EJ2" t="n">
         <v>15</v>
       </c>
-      <c r="EH2" t="n">
+      <c r="EK2" t="n">
         <v>15</v>
-      </c>
-      <c r="EI2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>-1.5837107</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>13.05</v>
       </c>
       <c r="EL2" t="inlineStr"/>
     </row>
